--- a/artfynd/A 7102-2025 artfynd.xlsx
+++ b/artfynd/A 7102-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101375901</v>
+        <v>101376031</v>
       </c>
       <c r="B2" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>61491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>106670</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Arion ater ater</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451597.2468161641</v>
+        <v>451493</v>
       </c>
       <c r="R2" t="n">
-        <v>6292448.234649378</v>
+        <v>6292225</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,24 +764,14 @@
           <t>2022-06-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-03</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>7 stänglar med knoppar. Barrskog.</t>
+          <t>Flera sedda i omgivningen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,15 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101375928</v>
+        <v>101375839</v>
       </c>
       <c r="B3" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,36 +810,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>82</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -865,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451699.7304234976</v>
+        <v>451584</v>
       </c>
       <c r="R3" t="n">
-        <v>6292336.360936564</v>
+        <v>6292466</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -898,24 +883,14 @@
           <t>2022-06-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-03</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Traktorväg</t>
+          <t>35 knoppstänglar. Barrskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -943,15 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101375839</v>
+        <v>101375901</v>
       </c>
       <c r="B4" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +948,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -999,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451584.2736540178</v>
+        <v>451597</v>
       </c>
       <c r="R4" t="n">
-        <v>6292465.9194583</v>
+        <v>6292448</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1032,24 +1002,14 @@
           <t>2022-06-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-03</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>35 knoppstänglar. Barrskog.</t>
+          <t>7 stänglar med knoppar. Barrskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1074,6 +1034,240 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>101375928</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ljusandal, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>451700</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6292336</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Agunnaryd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-06-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-06-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Traktorväg</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>101375954</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ljusandal, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>451738</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6292330</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Agunnaryd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-06-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-06-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Traktorväg</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7102-2025 artfynd.xlsx
+++ b/artfynd/A 7102-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101376031</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101375839</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1034,6 +1049,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101375901</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1153,6 +1173,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101375928</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1268,8 +1293,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101375954</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>